--- a/data/Data_expe_raw/Data_DENS.xlsx
+++ b/data/Data_expe_raw/Data_DENS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/Acali-DEB/data/Data_expe_raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7538F3A3-A266-3E4C-A523-8E4666DF0A1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794D1F89-B0D4-AC48-9B1D-6DA1D414AAFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-1980" windowWidth="38400" windowHeight="21100" xr2:uid="{1F865021-A1C9-49F8-B60B-9226F64A7D7C}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{1F865021-A1C9-49F8-B60B-9226F64A7D7C}"/>
   </bookViews>
   <sheets>
     <sheet name="Données manip densité" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Données manip densité'!$B$1:$L$775</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Feuil1!$A$1:$K$126</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -5132,7 +5133,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="50">
         <v>45826</v>
       </c>
@@ -5174,7 +5175,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="50">
         <v>45826</v>
       </c>
@@ -5216,7 +5217,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="50">
         <v>45826</v>
       </c>
@@ -5258,7 +5259,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="50">
         <v>45826</v>
       </c>
@@ -5300,7 +5301,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="50">
         <v>45826</v>
       </c>
@@ -5342,7 +5343,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="50">
         <v>45826</v>
       </c>
@@ -5384,7 +5385,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:13" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="58">
         <v>45826</v>
       </c>
@@ -5426,7 +5427,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="62">
         <v>45826</v>
       </c>
@@ -5468,7 +5469,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="63" spans="1:13" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:13" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="66">
         <v>45826</v>
       </c>
@@ -5510,7 +5511,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="62">
         <v>45826</v>
       </c>
@@ -5552,7 +5553,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="1:14" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="66">
         <v>45826</v>
       </c>
@@ -5594,7 +5595,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="62">
         <v>45826</v>
       </c>
@@ -5636,7 +5637,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="67" spans="1:14" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:14" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="66">
         <v>45826</v>
       </c>
@@ -5678,7 +5679,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="62">
         <v>45826</v>
       </c>
@@ -5720,7 +5721,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="69" spans="1:14" s="20" customFormat="1" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" s="20" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A69" s="78">
         <v>45826</v>
       </c>
@@ -8284,7 +8285,7 @@
       <c r="Z122" s="8"/>
       <c r="AA122" s="8"/>
     </row>
-    <row r="123" spans="1:27" s="96" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:27" s="96" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="50">
         <v>45840</v>
       </c>
@@ -8340,7 +8341,7 @@
       <c r="Z123"/>
       <c r="AA123"/>
     </row>
-    <row r="124" spans="1:27" s="96" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:27" s="96" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="50">
         <v>45840</v>
       </c>
@@ -8396,7 +8397,7 @@
       <c r="Z124"/>
       <c r="AA124"/>
     </row>
-    <row r="125" spans="1:27" s="96" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:27" s="96" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="50">
         <v>45840</v>
       </c>
@@ -8452,7 +8453,7 @@
       <c r="Z125"/>
       <c r="AA125"/>
     </row>
-    <row r="126" spans="1:27" s="96" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:27" s="96" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="50">
         <v>45840</v>
       </c>
@@ -8508,7 +8509,7 @@
       <c r="Z126"/>
       <c r="AA126"/>
     </row>
-    <row r="127" spans="1:27" s="96" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:27" s="96" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="50">
         <v>45840</v>
       </c>
@@ -8564,7 +8565,7 @@
       <c r="Z127"/>
       <c r="AA127"/>
     </row>
-    <row r="128" spans="1:27" s="96" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:27" s="96" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A128" s="50">
         <v>45840</v>
       </c>
@@ -8620,7 +8621,7 @@
       <c r="Z128"/>
       <c r="AA128"/>
     </row>
-    <row r="129" spans="1:27" s="97" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:27" s="97" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A129" s="58">
         <v>45840</v>
       </c>
@@ -8676,7 +8677,7 @@
       <c r="Z129" s="8"/>
       <c r="AA129" s="8"/>
     </row>
-    <row r="130" spans="1:27" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A130" s="62">
         <v>45840</v>
       </c>
@@ -8718,7 +8719,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="131" spans="1:27" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:27" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A131" s="66">
         <v>45840</v>
       </c>
@@ -8760,7 +8761,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="132" spans="1:27" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A132" s="62">
         <v>45840</v>
       </c>
@@ -8802,7 +8803,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="133" spans="1:27" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:27" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A133" s="66">
         <v>45840</v>
       </c>
@@ -8842,7 +8843,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="134" spans="1:27" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A134" s="62">
         <v>45840</v>
       </c>
@@ -8884,7 +8885,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="135" spans="1:27" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:27" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="66">
         <v>45840</v>
       </c>
@@ -8924,7 +8925,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="136" spans="1:27" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:27" ht="16" x14ac:dyDescent="0.2">
       <c r="A136" s="62">
         <v>45840</v>
       </c>
@@ -8966,7 +8967,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="137" spans="1:27" s="20" customFormat="1" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:27" s="20" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A137" s="78">
         <v>45840</v>
       </c>
@@ -11526,7 +11527,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="198" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:16" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A198" s="50">
         <v>45854</v>
       </c>
@@ -11568,7 +11569,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="199" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:16" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A199" s="50">
         <v>45854</v>
       </c>
@@ -11610,7 +11611,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="200" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:16" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A200" s="50">
         <v>45854</v>
       </c>
@@ -11652,7 +11653,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="201" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:16" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A201" s="50">
         <v>45854</v>
       </c>
@@ -11694,7 +11695,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="202" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:16" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A202" s="50">
         <v>45854</v>
       </c>
@@ -11736,7 +11737,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="203" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:16" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A203" s="50">
         <v>45854</v>
       </c>
@@ -11778,7 +11779,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="204" spans="1:16" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:16" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A204" s="58">
         <v>45854</v>
       </c>
@@ -11820,7 +11821,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="205" spans="1:16" s="115" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:16" s="115" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A205" s="62">
         <v>45854</v>
       </c>
@@ -11865,7 +11866,7 @@
       <c r="O205"/>
       <c r="P205"/>
     </row>
-    <row r="206" spans="1:16" s="120" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:16" s="120" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A206" s="66">
         <v>45854</v>
       </c>
@@ -11908,7 +11909,7 @@
       <c r="O206" s="8"/>
       <c r="P206" s="8"/>
     </row>
-    <row r="207" spans="1:16" s="115" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:16" s="115" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A207" s="62">
         <v>45854</v>
       </c>
@@ -11953,7 +11954,7 @@
       <c r="O207"/>
       <c r="P207"/>
     </row>
-    <row r="208" spans="1:16" s="120" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:16" s="120" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A208" s="66">
         <v>45854</v>
       </c>
@@ -11996,7 +11997,7 @@
       <c r="O208" s="8"/>
       <c r="P208" s="8"/>
     </row>
-    <row r="209" spans="1:16" s="115" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:16" s="115" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A209" s="62">
         <v>45854</v>
       </c>
@@ -12041,7 +12042,7 @@
       <c r="O209"/>
       <c r="P209"/>
     </row>
-    <row r="210" spans="1:16" s="120" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:16" s="120" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A210" s="66">
         <v>45854</v>
       </c>
@@ -12084,7 +12085,7 @@
       <c r="O210" s="8"/>
       <c r="P210" s="8"/>
     </row>
-    <row r="211" spans="1:16" s="115" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:16" s="115" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A211" s="62">
         <v>45854</v>
       </c>
@@ -12129,7 +12130,7 @@
       <c r="O211"/>
       <c r="P211"/>
     </row>
-    <row r="212" spans="1:16" s="120" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:16" s="120" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A212" s="66">
         <v>45854</v>
       </c>
@@ -12174,7 +12175,7 @@
       <c r="O212" s="8"/>
       <c r="P212" s="8"/>
     </row>
-    <row r="213" spans="1:16" s="115" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:16" s="115" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A213" s="62">
         <v>45854</v>
       </c>
@@ -12219,7 +12220,7 @@
       <c r="O213"/>
       <c r="P213"/>
     </row>
-    <row r="214" spans="1:16" s="120" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:16" s="120" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A214" s="66">
         <v>45854</v>
       </c>
@@ -12264,7 +12265,7 @@
       <c r="O214" s="8"/>
       <c r="P214" s="8"/>
     </row>
-    <row r="215" spans="1:16" s="115" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:16" s="115" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A215" s="62">
         <v>45854</v>
       </c>
@@ -12309,7 +12310,7 @@
       <c r="O215"/>
       <c r="P215"/>
     </row>
-    <row r="216" spans="1:16" s="120" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:16" s="120" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A216" s="66">
         <v>45854</v>
       </c>
@@ -12354,7 +12355,7 @@
       <c r="O216" s="8"/>
       <c r="P216" s="8"/>
     </row>
-    <row r="217" spans="1:16" s="115" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:16" s="115" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A217" s="62">
         <v>45854</v>
       </c>
@@ -12399,7 +12400,7 @@
       <c r="O217"/>
       <c r="P217"/>
     </row>
-    <row r="218" spans="1:16" s="128" customFormat="1" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:16" s="128" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A218" s="78">
         <v>45854</v>
       </c>
@@ -14672,7 +14673,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="272" spans="1:13" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:13" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A272" s="54">
         <v>45868</v>
       </c>
@@ -14714,7 +14715,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="273" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A273" s="50">
         <v>45868</v>
       </c>
@@ -14756,7 +14757,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="274" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A274" s="50">
         <v>45868</v>
       </c>
@@ -14798,7 +14799,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="275" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A275" s="50">
         <v>45868</v>
       </c>
@@ -14840,7 +14841,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="276" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A276" s="50">
         <v>45868</v>
       </c>
@@ -14882,7 +14883,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="277" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A277" s="50">
         <v>45868</v>
       </c>
@@ -14924,7 +14925,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="278" spans="1:14" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:14" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A278" s="58">
         <v>45868</v>
       </c>
@@ -14966,7 +14967,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="279" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A279" s="62">
         <v>45868</v>
       </c>
@@ -15008,7 +15009,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="280" spans="1:14" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:14" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A280" s="66">
         <v>45868</v>
       </c>
@@ -15048,7 +15049,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="281" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A281" s="62">
         <v>45868</v>
       </c>
@@ -15088,7 +15089,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="282" spans="1:14" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:14" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A282" s="66">
         <v>45868</v>
       </c>
@@ -15125,7 +15126,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="283" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A283" s="62">
         <v>45868</v>
       </c>
@@ -15167,7 +15168,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="284" spans="1:14" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:14" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A284" s="66">
         <v>45868</v>
       </c>
@@ -15209,7 +15210,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="285" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A285" s="62">
         <v>45868</v>
       </c>
@@ -15251,7 +15252,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="286" spans="1:14" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:14" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A286" s="66">
         <v>45868</v>
       </c>
@@ -17513,7 +17514,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="340" spans="1:13" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:13" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A340" s="54">
         <v>45882</v>
       </c>
@@ -17555,7 +17556,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="341" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A341" s="50">
         <v>45882</v>
       </c>
@@ -17597,7 +17598,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="342" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A342" s="50">
         <v>45882</v>
       </c>
@@ -17639,7 +17640,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="343" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A343" s="50">
         <v>45882</v>
       </c>
@@ -17681,7 +17682,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="344" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A344" s="50">
         <v>45882</v>
       </c>
@@ -17723,7 +17724,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="345" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A345" s="50">
         <v>45882</v>
       </c>
@@ -17765,7 +17766,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="346" spans="1:13" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:13" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A346" s="58">
         <v>45882</v>
       </c>
@@ -17807,7 +17808,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="347" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A347" s="62">
         <v>45882</v>
       </c>
@@ -17849,7 +17850,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="348" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A348" s="62">
         <v>45882</v>
       </c>
@@ -17889,7 +17890,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="349" spans="1:13" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:13" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A349" s="133">
         <v>45882</v>
       </c>
@@ -17931,7 +17932,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="350" spans="1:13" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:13" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A350" s="66">
         <v>45882</v>
       </c>
@@ -17971,7 +17972,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="351" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A351" s="62">
         <v>45882</v>
       </c>
@@ -18013,7 +18014,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="352" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A352" s="62">
         <v>45882</v>
       </c>
@@ -18055,7 +18056,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="353" spans="1:13" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:13" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A353" s="133">
         <v>45882</v>
       </c>
@@ -18097,7 +18098,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="354" spans="1:13" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:13" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A354" s="66">
         <v>45882</v>
       </c>
@@ -20423,7 +20424,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="408" spans="1:14" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:14" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A408" s="54">
         <v>45896</v>
       </c>
@@ -20468,7 +20469,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="409" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A409" s="50">
         <v>45896</v>
       </c>
@@ -20513,7 +20514,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="410" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A410" s="50">
         <v>45896</v>
       </c>
@@ -20558,7 +20559,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="411" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A411" s="50">
         <v>45896</v>
       </c>
@@ -20603,7 +20604,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="412" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A412" s="50">
         <v>45896</v>
       </c>
@@ -20648,7 +20649,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="413" spans="1:14" ht="16" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A413" s="50">
         <v>45896</v>
       </c>
@@ -20693,7 +20694,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="414" spans="1:14" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:14" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A414" s="58">
         <v>45896</v>
       </c>
@@ -20738,7 +20739,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="415" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A415" s="62">
         <v>45896</v>
       </c>
@@ -20780,7 +20781,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="416" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A416" s="62">
         <v>45896</v>
       </c>
@@ -20820,7 +20821,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="417" spans="1:14" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:14" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A417" s="133">
         <v>45896</v>
       </c>
@@ -20862,7 +20863,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="418" spans="1:14" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:14" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A418" s="66">
         <v>45896</v>
       </c>
@@ -20902,7 +20903,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="419" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A419" s="62">
         <v>45896</v>
       </c>
@@ -20944,7 +20945,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="420" spans="1:14" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A420" s="62">
         <v>45896</v>
       </c>
@@ -20986,7 +20987,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="421" spans="1:14" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:14" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A421" s="133">
         <v>45896</v>
       </c>
@@ -21028,7 +21029,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="422" spans="1:14" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:14" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A422" s="66">
         <v>45896</v>
       </c>
@@ -23249,7 +23250,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="475" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A475" s="50">
         <v>45910</v>
       </c>
@@ -23291,7 +23292,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="476" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A476" s="50">
         <v>45910</v>
       </c>
@@ -23333,7 +23334,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="477" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A477" s="50">
         <v>45910</v>
       </c>
@@ -23375,7 +23376,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="478" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A478" s="50">
         <v>45910</v>
       </c>
@@ -23417,7 +23418,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="479" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A479" s="50">
         <v>45910</v>
       </c>
@@ -23459,7 +23460,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="480" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A480" s="50">
         <v>45910</v>
       </c>
@@ -23501,7 +23502,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="481" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A481" s="50">
         <v>45910</v>
       </c>
@@ -23541,7 +23542,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="482" spans="1:13" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:13" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A482" s="133">
         <v>45910</v>
       </c>
@@ -23583,7 +23584,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="483" spans="1:13" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:13" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A483" s="66">
         <v>45910</v>
       </c>
@@ -23625,7 +23626,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="484" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A484" s="62">
         <v>45910</v>
       </c>
@@ -23667,7 +23668,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="485" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A485" s="62">
         <v>45910</v>
       </c>
@@ -25845,7 +25846,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="537" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A537" s="50">
         <v>45924</v>
       </c>
@@ -25887,7 +25888,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="538" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A538" s="50">
         <v>45924</v>
       </c>
@@ -25929,7 +25930,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="539" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="539" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A539" s="50">
         <v>45924</v>
       </c>
@@ -25971,7 +25972,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="540" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A540" s="50">
         <v>45924</v>
       </c>
@@ -26013,7 +26014,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="541" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A541" s="50">
         <v>45924</v>
       </c>
@@ -26055,7 +26056,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="542" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A542" s="50">
         <v>45924</v>
       </c>
@@ -26097,7 +26098,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="543" spans="1:13" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:13" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A543" s="133">
         <v>45924</v>
       </c>
@@ -26139,7 +26140,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="544" spans="1:13" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:13" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A544" s="66">
         <v>45924</v>
       </c>
@@ -26181,7 +26182,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="545" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A545" s="62">
         <v>45924</v>
       </c>
@@ -26223,7 +26224,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="546" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A546" s="62">
         <v>45924</v>
       </c>
@@ -28281,7 +28282,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="595" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A595" s="50">
         <v>45938</v>
       </c>
@@ -28323,7 +28324,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="596" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A596" s="50">
         <v>45938</v>
       </c>
@@ -28365,7 +28366,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="597" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A597" s="50">
         <v>45938</v>
       </c>
@@ -28407,7 +28408,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="598" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A598" s="50">
         <v>45938</v>
       </c>
@@ -28449,7 +28450,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="599" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A599" s="50">
         <v>45938</v>
       </c>
@@ -28491,7 +28492,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="600" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A600" s="50">
         <v>45938</v>
       </c>
@@ -28533,7 +28534,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="601" spans="1:13" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:13" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A601" s="133">
         <v>45938</v>
       </c>
@@ -28575,7 +28576,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="602" spans="1:13" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:13" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A602" s="66">
         <v>45938</v>
       </c>
@@ -28617,7 +28618,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="603" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A603" s="62">
         <v>45938</v>
       </c>
@@ -28659,7 +28660,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="604" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A604" s="62">
         <v>45938</v>
       </c>
@@ -30675,7 +30676,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="652" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A652" s="50">
         <v>45952</v>
       </c>
@@ -30717,7 +30718,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="653" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A653" s="50">
         <v>45952</v>
       </c>
@@ -30759,7 +30760,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="654" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A654" s="50">
         <v>45952</v>
       </c>
@@ -30801,7 +30802,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="655" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A655" s="50">
         <v>45952</v>
       </c>
@@ -30843,7 +30844,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="656" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A656" s="50">
         <v>45952</v>
       </c>
@@ -30885,7 +30886,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="657" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A657" s="50">
         <v>45952</v>
       </c>
@@ -30927,7 +30928,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="658" spans="1:13" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:13" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A658" s="133">
         <v>45952</v>
       </c>
@@ -30969,7 +30970,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="659" spans="1:13" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:13" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A659" s="66">
         <v>45952</v>
       </c>
@@ -31011,7 +31012,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="660" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A660" s="62">
         <v>45952</v>
       </c>
@@ -31053,7 +31054,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="661" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A661" s="62">
         <v>45952</v>
       </c>
@@ -33069,7 +33070,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="709" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A709" s="50">
         <v>45966</v>
       </c>
@@ -33111,7 +33112,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="710" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A710" s="50">
         <v>45966</v>
       </c>
@@ -33153,7 +33154,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="711" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A711" s="50">
         <v>45966</v>
       </c>
@@ -33195,7 +33196,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="712" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A712" s="50">
         <v>45966</v>
       </c>
@@ -33237,7 +33238,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="713" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A713" s="50">
         <v>45966</v>
       </c>
@@ -33279,7 +33280,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="714" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="714" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A714" s="50">
         <v>45966</v>
       </c>
@@ -33321,7 +33322,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="715" spans="1:13" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="1:13" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A715" s="133">
         <v>45966</v>
       </c>
@@ -33363,7 +33364,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="716" spans="1:13" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="1:13" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A716" s="66">
         <v>45966</v>
       </c>
@@ -33405,7 +33406,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="717" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A717" s="62">
         <v>45966</v>
       </c>
@@ -33447,7 +33448,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="718" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A718" s="62">
         <v>45966</v>
       </c>
@@ -35461,7 +35462,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="766" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="766" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A766" s="50">
         <v>45980</v>
       </c>
@@ -35503,7 +35504,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="767" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="767" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A767" s="50">
         <v>45980</v>
       </c>
@@ -35545,7 +35546,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="768" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="768" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A768" s="50">
         <v>45980</v>
       </c>
@@ -35587,7 +35588,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="769" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="769" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A769" s="50">
         <v>45980</v>
       </c>
@@ -35629,7 +35630,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="770" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="770" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A770" s="50">
         <v>45980</v>
       </c>
@@ -35671,7 +35672,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="771" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="771" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
       <c r="A771" s="50">
         <v>45980</v>
       </c>
@@ -35713,7 +35714,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="772" spans="1:13" s="34" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="1:13" s="34" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A772" s="133">
         <v>45980</v>
       </c>
@@ -35755,7 +35756,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="773" spans="1:13" s="8" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="1:13" s="8" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A773" s="66">
         <v>45980</v>
       </c>
@@ -35797,7 +35798,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="774" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A774" s="62">
         <v>45980</v>
       </c>
@@ -35839,7 +35840,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="775" spans="1:13" ht="16" hidden="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="1:13" ht="16" x14ac:dyDescent="0.2">
       <c r="A775" s="62">
         <v>45980</v>
       </c>
@@ -35885,17 +35886,7 @@
   <autoFilter ref="B1:L775" xr:uid="{7A989BE5-CF0D-4354-BC94-FA2AAA6A8EB4}">
     <filterColumn colId="6">
       <filters>
-        <filter val="D7"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="7">
-      <filters>
-        <filter val="4"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="8">
-      <filters>
-        <filter val="A"/>
+        <filter val="D2b"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:L720">
@@ -35911,6 +35902,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A486AFCD-BF4B-1447-B360-B662B8741FD8}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K126"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -35954,7 +35946,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>45826</v>
       </c>
@@ -35990,7 +35982,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>45826</v>
       </c>
@@ -36026,7 +36018,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" s="6">
         <v>45826</v>
       </c>
@@ -36062,7 +36054,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" s="6">
         <v>45826</v>
       </c>
@@ -36098,7 +36090,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6">
         <v>45826</v>
       </c>
@@ -36134,7 +36126,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6">
         <v>45826</v>
       </c>
@@ -36170,7 +36162,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6">
         <v>45826</v>
       </c>
@@ -36206,7 +36198,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6">
         <v>45826</v>
       </c>
@@ -36386,7 +36378,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" s="6">
         <v>45826</v>
       </c>
@@ -36422,7 +36414,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" s="6">
         <v>45826</v>
       </c>
@@ -36458,7 +36450,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16" s="6">
         <v>45826</v>
       </c>
@@ -36494,7 +36486,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17" s="6">
         <v>45826</v>
       </c>
@@ -36530,7 +36522,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18" s="6">
         <v>45826</v>
       </c>
@@ -36566,7 +36558,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="6">
         <v>45826</v>
       </c>
@@ -36602,7 +36594,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20" s="6">
         <v>45826</v>
       </c>
@@ -36638,7 +36630,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>45826</v>
       </c>
@@ -36674,7 +36666,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="6">
         <v>45854</v>
       </c>
@@ -36710,7 +36702,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" s="6">
         <v>45854</v>
       </c>
@@ -36746,7 +36738,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" s="6">
         <v>45854</v>
       </c>
@@ -36782,7 +36774,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
         <v>45854</v>
       </c>
@@ -36818,7 +36810,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="6">
         <v>45854</v>
       </c>
@@ -36854,7 +36846,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
         <v>45854</v>
       </c>
@@ -36890,7 +36882,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
         <v>45854</v>
       </c>
@@ -36926,7 +36918,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
         <v>45854</v>
       </c>
@@ -37214,7 +37206,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6">
         <v>45854</v>
       </c>
@@ -37250,7 +37242,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
         <v>45854</v>
       </c>
@@ -37286,7 +37278,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
         <v>45854</v>
       </c>
@@ -37322,7 +37314,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
         <v>45854</v>
       </c>
@@ -37358,7 +37350,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
         <v>45854</v>
       </c>
@@ -37394,7 +37386,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6">
         <v>45854</v>
       </c>
@@ -37430,7 +37422,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6">
         <v>45854</v>
       </c>
@@ -37466,7 +37458,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="44" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:11" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
         <v>45854</v>
       </c>
@@ -37502,7 +37494,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6">
         <v>45882</v>
       </c>
@@ -37538,7 +37530,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6">
         <v>45882</v>
       </c>
@@ -37574,7 +37566,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
         <v>45882</v>
       </c>
@@ -37610,7 +37602,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6">
         <v>45882</v>
       </c>
@@ -37646,7 +37638,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6">
         <v>45882</v>
       </c>
@@ -37682,7 +37674,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50" s="6">
         <v>45882</v>
       </c>
@@ -37718,7 +37710,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="6">
         <v>45882</v>
       </c>
@@ -37754,7 +37746,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52" s="6">
         <v>45882</v>
       </c>
@@ -37862,7 +37854,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
         <v>45882</v>
       </c>
@@ -37898,7 +37890,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
         <v>45882</v>
       </c>
@@ -37934,7 +37926,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
         <v>45882</v>
       </c>
@@ -37970,7 +37962,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
         <v>45882</v>
       </c>
@@ -38006,7 +37998,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
         <v>45882</v>
       </c>
@@ -38042,7 +38034,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A60" s="6">
         <v>45882</v>
       </c>
@@ -38078,7 +38070,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A61" s="6">
         <v>45882</v>
       </c>
@@ -38114,7 +38106,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="62" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>45882</v>
       </c>
@@ -38150,7 +38142,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A63" s="6">
         <v>45910</v>
       </c>
@@ -38186,7 +38178,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64" s="6">
         <v>45910</v>
       </c>
@@ -38222,7 +38214,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A65" s="6">
         <v>45910</v>
       </c>
@@ -38259,7 +38251,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="6">
         <v>45910</v>
       </c>
@@ -38296,7 +38288,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A67" s="6">
         <v>45910</v>
       </c>
@@ -38333,7 +38325,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6">
         <v>45910</v>
       </c>
@@ -38444,7 +38436,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="6">
         <v>45910</v>
       </c>
@@ -38481,7 +38473,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="6">
         <v>45910</v>
       </c>
@@ -38518,7 +38510,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A73" s="6">
         <v>45910</v>
       </c>
@@ -38555,7 +38547,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74" s="6">
         <v>45910</v>
       </c>
@@ -38592,7 +38584,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="6">
         <v>45910</v>
       </c>
@@ -38629,7 +38621,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="6">
         <v>45910</v>
       </c>
@@ -38666,7 +38658,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A77" s="6">
         <v>45910</v>
       </c>
@@ -38703,7 +38695,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="78" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A78" s="7">
         <v>45910</v>
       </c>
@@ -38740,7 +38732,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A79" s="6">
         <v>45938</v>
       </c>
@@ -38776,7 +38768,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A80" s="6">
         <v>45938</v>
       </c>
@@ -38812,7 +38804,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81" s="6">
         <v>45938</v>
       </c>
@@ -38849,7 +38841,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82" s="6">
         <v>45938</v>
       </c>
@@ -38886,7 +38878,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83" s="6">
         <v>45938</v>
       </c>
@@ -38923,7 +38915,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84" s="6">
         <v>45938</v>
       </c>
@@ -39034,7 +39026,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87" s="6">
         <v>45938</v>
       </c>
@@ -39071,7 +39063,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88" s="6">
         <v>45938</v>
       </c>
@@ -39108,7 +39100,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89" s="6">
         <v>45938</v>
       </c>
@@ -39145,7 +39137,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90" s="6">
         <v>45938</v>
       </c>
@@ -39182,7 +39174,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="6">
         <v>45938</v>
       </c>
@@ -39219,7 +39211,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A92" s="6">
         <v>45938</v>
       </c>
@@ -39256,7 +39248,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="6">
         <v>45938</v>
       </c>
@@ -39293,7 +39285,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="94" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="7">
         <v>45938</v>
       </c>
@@ -39330,7 +39322,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="6">
         <v>45966</v>
       </c>
@@ -39366,7 +39358,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="6">
         <v>45966</v>
       </c>
@@ -39402,7 +39394,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97" s="6">
         <v>45966</v>
       </c>
@@ -39439,7 +39431,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="6">
         <v>45966</v>
       </c>
@@ -39476,7 +39468,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99" s="6">
         <v>45966</v>
       </c>
@@ -39513,7 +39505,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100" s="6">
         <v>45966</v>
       </c>
@@ -39624,7 +39616,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A103" s="6">
         <v>45966</v>
       </c>
@@ -39661,7 +39653,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="6">
         <v>45966</v>
       </c>
@@ -39698,7 +39690,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="6">
         <v>45966</v>
       </c>
@@ -39735,7 +39727,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106" s="6">
         <v>45966</v>
       </c>
@@ -39772,7 +39764,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="6">
         <v>45966</v>
       </c>
@@ -39809,7 +39801,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="6">
         <v>45966</v>
       </c>
@@ -39846,7 +39838,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A109" s="6">
         <v>45966</v>
       </c>
@@ -39883,7 +39875,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="110" spans="1:11" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" s="8" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <v>45966</v>
       </c>
@@ -39920,7 +39912,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A111" s="6">
         <v>45980</v>
       </c>
@@ -39956,7 +39948,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="6">
         <v>45980</v>
       </c>
@@ -39992,7 +39984,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="6">
         <v>45981</v>
       </c>
@@ -40029,7 +40021,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A114" s="6">
         <v>45982</v>
       </c>
@@ -40066,7 +40058,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A115" s="6">
         <v>45983</v>
       </c>
@@ -40103,7 +40095,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="6">
         <v>45984</v>
       </c>
@@ -40214,7 +40206,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="6">
         <v>45987</v>
       </c>
@@ -40251,7 +40243,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="6">
         <v>45988</v>
       </c>
@@ -40288,7 +40280,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="6">
         <v>45989</v>
       </c>
@@ -40325,7 +40317,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="6">
         <v>45990</v>
       </c>
@@ -40362,7 +40354,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="6">
         <v>45991</v>
       </c>
@@ -40399,7 +40391,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="6">
         <v>45992</v>
       </c>
@@ -40436,7 +40428,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="6">
         <v>45993</v>
       </c>
@@ -40473,7 +40465,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="6">
         <v>45966</v>
       </c>
@@ -40511,6 +40503,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K126" xr:uid="{A486AFCD-BF4B-1447-B360-B662B8741FD8}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="D2b"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
